--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>135646818</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>135646819</v>
       </c>
       <c r="B11" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>135646824</v>
       </c>
       <c r="B12" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>135646832</v>
       </c>
       <c r="B13" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>135646828</v>
       </c>
       <c r="B14" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>135646839</v>
       </c>
       <c r="B15" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92408</v>
+        <v>92435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92400</v>
+        <v>92402</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92440</v>
+        <v>92442</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>92000</v>
+        <v>92014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92402</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135646818</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>135646819</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>135646824</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135646832</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>135646828</v>
       </c>
       <c r="B14" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135646839</v>
       </c>
       <c r="B15" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135646820</v>
       </c>
       <c r="B16" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>135646821</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>135646823</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135646829</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135646837</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135646841</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135646842</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135646844</v>
       </c>
       <c r="B23" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135646850</v>
       </c>
       <c r="B24" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135646851</v>
       </c>
       <c r="B25" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135646852</v>
       </c>
       <c r="B26" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>135646856</v>
       </c>
       <c r="B27" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135646862</v>
       </c>
       <c r="B28" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>135646863</v>
       </c>
       <c r="B29" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>135646864</v>
       </c>
       <c r="B30" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135646897</v>
       </c>
       <c r="B31" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135646905</v>
       </c>
       <c r="B32" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92442</v>
+        <v>92456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>92014</v>
+        <v>92015</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92415</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135646818</v>
       </c>
       <c r="B10" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>135646819</v>
       </c>
       <c r="B11" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>135646824</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135646832</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>135646828</v>
       </c>
       <c r="B14" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135646839</v>
       </c>
       <c r="B15" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92456</v>
+        <v>92457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>92015</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92415</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92457</v>
+        <v>92458</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92062</v>
+        <v>92063</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135646818</v>
       </c>
       <c r="B10" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>135646819</v>
       </c>
       <c r="B11" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>135646824</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135646832</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>135646828</v>
       </c>
       <c r="B14" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135646839</v>
       </c>
       <c r="B15" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135646820</v>
       </c>
       <c r="B16" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>135646821</v>
       </c>
       <c r="B17" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>135646823</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135646829</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135646837</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135646841</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135646842</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135646844</v>
       </c>
       <c r="B23" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135646850</v>
       </c>
       <c r="B24" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135646851</v>
       </c>
       <c r="B25" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135646852</v>
       </c>
       <c r="B26" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>135646856</v>
       </c>
       <c r="B27" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135646862</v>
       </c>
       <c r="B28" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>135646863</v>
       </c>
       <c r="B29" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>135646864</v>
       </c>
       <c r="B30" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135646897</v>
       </c>
       <c r="B31" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135646905</v>
       </c>
       <c r="B32" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92458</v>
+        <v>92459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135646834</v>
       </c>
       <c r="B2" t="n">
-        <v>92017</v>
+        <v>92023</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135646858</v>
       </c>
       <c r="B3" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135646860</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135646895</v>
       </c>
       <c r="B5" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135646899</v>
       </c>
       <c r="B6" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135646838</v>
       </c>
       <c r="B7" t="n">
-        <v>92063</v>
+        <v>92069</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135646900</v>
       </c>
       <c r="B8" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92417</v>
+        <v>92423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>135646818</v>
       </c>
       <c r="B10" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>135646819</v>
       </c>
       <c r="B11" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>135646824</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>135646832</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>135646828</v>
       </c>
       <c r="B14" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>135646839</v>
       </c>
       <c r="B15" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>135646820</v>
       </c>
       <c r="B16" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
         <v>135646821</v>
       </c>
       <c r="B17" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
         <v>135646823</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135646829</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>135646837</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>135646841</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>135646842</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
         <v>135646844</v>
       </c>
       <c r="B23" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>135646850</v>
       </c>
       <c r="B24" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>135646851</v>
       </c>
       <c r="B25" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>135646852</v>
       </c>
       <c r="B26" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3597,7 +3597,7 @@
         <v>135646856</v>
       </c>
       <c r="B27" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>135646862</v>
       </c>
       <c r="B28" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>135646863</v>
       </c>
       <c r="B29" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>135646864</v>
       </c>
       <c r="B30" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>135646897</v>
       </c>
       <c r="B31" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>135646905</v>
       </c>
       <c r="B32" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>135646902</v>
       </c>
       <c r="B33" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>135646859</v>
       </c>
       <c r="B34" t="n">
-        <v>92459</v>
+        <v>92465</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92423</v>
+        <v>92424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92424</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 28898-2026 artfynd.xlsx
+++ b/artfynd/A 28898-2026 artfynd.xlsx
@@ -1467,7 +1467,7 @@
         <v>135646836</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
